--- a/Source/Tesla/Documentation/Tesla Plant Matrix.xlsx
+++ b/Source/Tesla/Documentation/Tesla Plant Matrix.xlsx
@@ -4,17 +4,52 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="29010" yWindow="-75" windowWidth="23250" windowHeight="12525"/>
+    <workbookView xWindow="29016" yWindow="-12" windowWidth="23256" windowHeight="12468" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Fremont" sheetId="13" r:id="rId1"/>
+    <sheet name="Tilburg" sheetId="14" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Joseph Wynia</author>
+  </authors>
+  <commentList>
+    <comment ref="A19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Joseph Wynia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Moved to Tilburg</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="70">
   <si>
     <t>192.168.1.1</t>
   </si>
@@ -188,13 +223,49 @@
   </si>
   <si>
     <t>/Common3700/Source/Tesla/Burke_PorterCCRT</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Tesla_Freemont_507560</t>
+  </si>
+  <si>
+    <t>Tilburg</t>
+  </si>
+  <si>
+    <t>Tilburg, Netherlands</t>
+  </si>
+  <si>
+    <t>Tesla_3700.ccrt.rtos</t>
+  </si>
+  <si>
+    <t>192.168.1.20</t>
+  </si>
+  <si>
+    <t>192.168.1.21</t>
+  </si>
+  <si>
+    <t>Ccrt/branches/Common3700</t>
+  </si>
+  <si>
+    <t>Ccrt/branches/Common3700/Source/Tesla/Burke_PorterCCRT</t>
+  </si>
+  <si>
+    <t>Ccrt-C09061508</t>
+  </si>
+  <si>
+    <t>last change 21847</t>
+  </si>
+  <si>
+    <t>last change 21738</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,13 +297,32 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -442,7 +532,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -541,6 +631,25 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -843,26 +952,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -895,7 +1004,7 @@
       <c r="F3" s="16"/>
       <c r="G3" s="22"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B4" s="35"/>
       <c r="C4" s="2"/>
       <c r="D4" s="5"/>
@@ -903,7 +1012,7 @@
       <c r="F4" s="16"/>
       <c r="G4" s="22"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="5"/>
       <c r="D5" s="17"/>
@@ -911,7 +1020,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="22"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -919,7 +1028,7 @@
       <c r="F6" s="16"/>
       <c r="G6" s="22"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="B7" s="22"/>
       <c r="F7" s="16"/>
       <c r="G7" s="22"/>
@@ -936,25 +1045,25 @@
       <c r="E9" s="23"/>
       <c r="F9" s="26"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="F10" s="16"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="F11" s="16"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="F12" s="16"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="F13" s="16"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="F15" s="16"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>24</v>
       </c>
@@ -1016,47 +1125,45 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15">
+    <row r="19" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="42"/>
+      <c r="B19" s="43">
+        <v>507211</v>
+      </c>
+      <c r="C19" s="44">
+        <v>3700</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="38">
-        <v>507211</v>
-      </c>
-      <c r="C19" s="29">
-        <v>3700</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5" t="s">
+      <c r="G19" s="45"/>
+      <c r="H19" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36" t="s">
+      <c r="I19" s="46"/>
+      <c r="J19" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="K19" s="36" t="s">
+      <c r="K19" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
       <c r="R19" s="22"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12">
-        <v>2</v>
+      <c r="A20" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="B20" s="36">
         <v>507560</v>
@@ -1081,7 +1188,9 @@
         <v>47</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="36"/>
+      <c r="M20" s="36" t="s">
+        <v>59</v>
+      </c>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
       <c r="P20" s="16"/>
@@ -1089,8 +1198,8 @@
       <c r="R20" s="22"/>
     </row>
     <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
-        <v>3</v>
+      <c r="A21" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="B21" s="36">
         <v>508180</v>
@@ -1135,9 +1244,9 @@
       </c>
       <c r="R21" s="22"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
-        <v>4</v>
+    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="48" t="s">
+        <v>58</v>
       </c>
       <c r="B22" s="36">
         <v>508202</v>
@@ -1221,7 +1330,7 @@
       <c r="Q24" s="16"/>
       <c r="R24" s="22"/>
     </row>
-    <row r="25" spans="1:18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1243,7 +1352,7 @@
       <c r="Q25" s="16"/>
       <c r="R25" s="22"/>
     </row>
-    <row r="26" spans="1:18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="15"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1265,7 +1374,7 @@
       <c r="Q26" s="16"/>
       <c r="R26" s="22"/>
     </row>
-    <row r="27" spans="1:18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="15"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1285,7 +1394,7 @@
       <c r="Q27" s="16"/>
       <c r="R27" s="22"/>
     </row>
-    <row r="28" spans="1:18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1305,7 +1414,7 @@
       <c r="Q28" s="16"/>
       <c r="R28" s="22"/>
     </row>
-    <row r="29" spans="1:18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1323,7 +1432,7 @@
       <c r="Q29" s="16"/>
       <c r="R29" s="22"/>
     </row>
-    <row r="30" spans="1:18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1363,7 +1472,7 @@
       <c r="Q31" s="16"/>
       <c r="R31" s="22"/>
     </row>
-    <row r="32" spans="1:18" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
       <c r="D32" s="26"/>
@@ -1381,12 +1490,12 @@
       <c r="P32" s="26"/>
       <c r="Q32" s="23"/>
     </row>
-    <row r="35" spans="1:11" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:11" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>15</v>
@@ -1427,7 +1536,7 @@
       <c r="J38" s="26"/>
       <c r="K38" s="22"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="33" t="s">
         <v>21</v>
       </c>
@@ -1441,7 +1550,7 @@
       <c r="J39" s="16"/>
       <c r="K39" s="22"/>
     </row>
-    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="33" t="s">
         <v>20</v>
       </c>
@@ -1460,7 +1569,7 @@
       <c r="J40" s="16"/>
       <c r="K40" s="22"/>
     </row>
-    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>14</v>
       </c>
@@ -1479,7 +1588,7 @@
       <c r="J41" s="16"/>
       <c r="K41" s="22"/>
     </row>
-    <row r="42" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="14"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -1492,7 +1601,7 @@
       <c r="J42" s="16"/>
       <c r="K42" s="22"/>
     </row>
-    <row r="43" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>
       <c r="B43" s="2"/>
       <c r="D43" s="17"/>
@@ -1504,7 +1613,7 @@
       <c r="J43" s="16"/>
       <c r="K43" s="22"/>
     </row>
-    <row r="44" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
       <c r="B44" s="2"/>
       <c r="D44" s="17"/>
@@ -1516,7 +1625,7 @@
       <c r="J44" s="16"/>
       <c r="K44" s="22"/>
     </row>
-    <row r="45" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>
       <c r="B45" s="2"/>
       <c r="D45" s="17"/>
@@ -1528,7 +1637,7 @@
       <c r="J45" s="16"/>
       <c r="K45" s="22"/>
     </row>
-    <row r="46" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>
       <c r="B46" s="2"/>
       <c r="D46" s="17"/>
@@ -1540,7 +1649,7 @@
       <c r="J46" s="16"/>
       <c r="K46" s="22"/>
     </row>
-    <row r="47" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>
       <c r="B47" s="2"/>
       <c r="D47" s="17"/>
@@ -1552,7 +1661,7 @@
       <c r="J47" s="16"/>
       <c r="K47" s="22"/>
     </row>
-    <row r="48" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>
       <c r="B48" s="2"/>
       <c r="D48" s="17"/>
@@ -1564,7 +1673,7 @@
       <c r="J48" s="16"/>
       <c r="K48" s="22"/>
     </row>
-    <row r="49" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>
       <c r="B49" s="2"/>
       <c r="D49" s="17"/>
@@ -1576,7 +1685,7 @@
       <c r="J49" s="16"/>
       <c r="K49" s="22"/>
     </row>
-    <row r="50" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -1589,7 +1698,7 @@
       <c r="J50" s="31"/>
       <c r="K50" s="22"/>
     </row>
-    <row r="51" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B51" s="23"/>
       <c r="C51" s="23"/>
       <c r="D51" s="23"/>
@@ -1600,7 +1709,7 @@
       <c r="I51" s="26"/>
       <c r="J51" s="23"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>25</v>
       </c>
@@ -1612,5 +1721,724 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="20"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="35"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="7"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="22"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="7"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="22"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="22"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="22"/>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="32"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="22"/>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="26"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="16"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="16"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12" s="16"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="16"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="16"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="17"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8"/>
+    </row>
+    <row r="18" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="N18" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="15">
+        <v>1</v>
+      </c>
+      <c r="B19" s="38">
+        <v>507211</v>
+      </c>
+      <c r="C19" s="29">
+        <v>3700</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="L19" s="5">
+        <v>507211</v>
+      </c>
+      <c r="M19" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q19" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="R19" s="22"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="12"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="22"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="12"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="37"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="22"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="14"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="37"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="22"/>
+    </row>
+    <row r="23" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="13"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="22"/>
+    </row>
+    <row r="24" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="15"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="22"/>
+    </row>
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="15"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="36"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="22"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="15"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="22"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="15"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="22"/>
+    </row>
+    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="12"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="22"/>
+    </row>
+    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="12"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="22"/>
+    </row>
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="22"/>
+    </row>
+    <row r="31" spans="1:18" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="13"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="22"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="23"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="19"/>
+    </row>
+    <row r="38" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="22"/>
+    </row>
+    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="22"/>
+    </row>
+    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="27"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="22"/>
+    </row>
+    <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="36"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="22"/>
+    </row>
+    <row r="42" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="14"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="22"/>
+    </row>
+    <row r="43" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="13"/>
+      <c r="B43" s="2"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="22"/>
+    </row>
+    <row r="44" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="13"/>
+      <c r="B44" s="2"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="22"/>
+    </row>
+    <row r="45" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="13"/>
+      <c r="B45" s="2"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="22"/>
+    </row>
+    <row r="46" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="13"/>
+      <c r="B46" s="2"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="22"/>
+    </row>
+    <row r="47" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="13"/>
+      <c r="B47" s="2"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="22"/>
+    </row>
+    <row r="48" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="13"/>
+      <c r="B48" s="2"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="22"/>
+    </row>
+    <row r="49" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="13"/>
+      <c r="B49" s="2"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="22"/>
+    </row>
+    <row r="50" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="13"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="31"/>
+      <c r="K50" s="22"/>
+    </row>
+    <row r="51" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="23"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="23"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B40" r:id="rId1"/>
+    <hyperlink ref="C40" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>